--- a/backend/data/seed_data_template.xlsx
+++ b/backend/data/seed_data_template.xlsx
@@ -15,6 +15,8 @@
     <sheet name="public_persons" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="media_descriptions" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="video_files" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="content_lists" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="screen_contents" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,6 +545,165 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>is_active</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>display_order</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>content_lists</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>screen_type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>_ref_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Homepage Layout</t>
+        </is>
+      </c>
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Main homepage screen layout with trending content</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Trending K-Dramas, Top Episodes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>homepage</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Homepage</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Drama Category Page</t>
+        </is>
+      </c>
+      <c r="B3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Drama category page showing featured and trending dramas</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Featured Content, Trending K-Dramas</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Drama Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Search Results Layout</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Layout for search results pages</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Top Episodes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Search Results</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1809,4 +1970,184 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>thumbnail_format</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>is_active</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>display_order</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>content_items</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>content_types</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>_ref_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Trending K-Dramas</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>large_landscape</t>
+        </is>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Most popular Korean drama series this month</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Squid Game, Kingdom, Crash Landing on You</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>["program", "program", "program"]</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Trending K-Dramas</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Top Episodes This Week</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>medium_portrait</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Most watched episodes from the past week</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Squid Game E01, Squid Game E02</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>["media_description", "media_description"]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Top Episodes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Featured Content</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>small_square</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Curated selection of featured content</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Squid Game, Squid Game E01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>["program", "media_description"]</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Featured Content</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>